--- a/promptDB/Photography.xlsx
+++ b/promptDB/Photography.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>원본 경로</t>
+          <t>메모</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -540,7 +540,6 @@
           <t>flux guidance 2.5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>euler</t>
@@ -585,8 +584,6 @@
       <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>euler</t>
@@ -631,8 +628,6 @@
       <c r="H4" t="n">
         <v>3.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>dpmpp_2m</t>

--- a/promptDB/Photography.xlsx
+++ b/promptDB/Photography.xlsx
@@ -128,6 +128,61 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1219200" cy="1219200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -417,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -504,41 +559,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00</t>
+          <t>2026-07-28 06:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>portrait of a woman, 85mm lens, shallow depth of field, natural window light, film grain, kodak portra 400</t>
+          <t>huge breast, boobs, lina face, A young woman with shoulder-length, wavy pink hair and bangs, wearing a white short-sleeved T-shirt featuring a vibrant anime-style graphic of two girls—one with long blue hair in a black blazer and the other with short black hair in a pink T-shirt—both wearing headphones and surrounded by floating iridescent bubbles, stands against a plain light gray background; she has bright blue eyes, subtle makeup including glossy lips, and wears high-waisted bright pink pants with a visible belt loop, her right hand resting on her hip while her left arm is slightly bent at the elbow, adorned with multiple thin metallic bangles on her wrist.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>oversaturated, plastic skin, cgi, cartoon, harsh flash</t>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>flux1-dev.safetensors</t>
+          <t>Krea2\krea2_turbo_int8_convrot.safetensors</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>190283746</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>flux guidance 2.5</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -547,43 +597,45 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00</t>
+          <t>2026-07-28 14:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>landscape photography, misty mountain valley at dawn, long exposure, wide angle, high dynamic range</t>
+          <t>she has huge breast(boobs), lina face, A close-up portrait of a young woman with dark, flowing hair partially framing her face, adorned with vibrant red flowers—some blooming, some as buds—woven into her strands and resting against her cheek; she gazes softly toward the viewer with large, expressive blue eyes that reflect sunlight, her lips curved in a gentle smile, her skin glowing with warm light; she wears a translucent, sheer blue garment that drapes over her shoulders and upper body, revealing hints of a darker underlayer beneath; beside her, a cluster of similar red flowers with green stems and leaves rises from the lower frame, their petals detailed with subtle gradients and highlights; behind her, a bright blue sky filled with fluffy white clouds stretches above a distant shoreline and ocean, with scattered flower petals floating midair near the top right corner; the overall composition is rendered in a vivid, painterly anime style with saturated colors, soft lighting, and a shallow depth of field that blurs the background into bokeh, emphasizing the subject’s serene expression and the floral details.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hdr halo, oversharpened, noise, tilted horizon</t>
+          <t>Exposed breasts, nipples, areolas, nakedness, nudity, nude, naked, cut face</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>flux1-dev.safetensors</t>
+          <t>Krea2\krea2_turbo_int8_convrot.safetensors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>700118234</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>euler</t>
@@ -591,55 +643,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>beta</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-28 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>product shot of a ceramic coffee cup, seamless grey backdrop, three point studio lighting, soft shadow, commercial photography</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>reflection of photographer, dust, fingerprints, clutter</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>flux1-dev.safetensors</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>33912055</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>dpmpp_2m</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>simple</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>